--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbf8ce6d949a54f9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re04ee69181894b07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1401496b0c994dd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a68c1e60355458b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re04ee69181894b07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6c4e9466a2874621"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a68c1e60355458b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1cd118a669441e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6c4e9466a2874621"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3bf03341d72540b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1cd118a669441e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e016b3de7644f92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3bf03341d72540b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re8f0b7a2ab98450e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e016b3de7644f92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc9b59d8cc20445e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re8f0b7a2ab98450e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R58a20758c178407d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc9b59d8cc20445e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree5c977421194ef4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R58a20758c178407d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc415bad37b7442ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree5c977421194ef4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb24bf3e7343b4438"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc415bad37b7442ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d4e1b1d81004210"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb24bf3e7343b4438"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40d6cecfea6548b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d4e1b1d81004210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf8eedaa85e174c0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40d6cecfea6548b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f29635c75a94e21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf8eedaa85e174c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rac523fdf3cce48b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f29635c75a94e21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f15322b3cb74012"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rac523fdf3cce48b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e5e386e10d34afe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f15322b3cb74012"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdca5df25066c47f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e5e386e10d34afe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d925330bdd8491a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdca5df25066c47f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cb83dff355c47ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d925330bdd8491a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6a2b17f18f5b4a1a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cb83dff355c47ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97093f27fe3842ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6a2b17f18f5b4a1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d0592a8951e4756"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97093f27fe3842ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3574ca955acf4e39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d0592a8951e4756"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R526cbd01cbf84726"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3574ca955acf4e39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc41273527a424c8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>